--- a/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Operations/Kafka_Operations.xlsx
+++ b/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Operations/Kafka_Operations.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kafka Operations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A) kafka-topics --list</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -486,10 +486,9 @@
           <t>A topic has a replication factor of 3 but one replica is out of sync. What command would you use to check the ISR status?</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kafka-topics --describe --topic &lt;topic_name&gt;</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -509,10 +508,9 @@
           <t>What tool is used to monitor consumer lag?</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>kafka-consumer-groups</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -539,7 +537,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B) Use kafka-topics --alter</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -559,10 +557,9 @@
           <t>A broker is being decommissioned. What is the safe process to migrate partitions?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Use kafka-reassign-partitions to move data to other brokers</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -582,10 +579,9 @@
           <t>What JMX metric indicates the rate of messages being produced?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>kafka.server:type=BrokerTopicMetrics,name=MessagesInPerSec</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -612,7 +608,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B) kafka-broker-api-versions</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -632,10 +628,9 @@
           <t>Consumer lag is increasing rapidly. What are two possible causes?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1) Consumer processing is slow 2) Producer throughput exceeded consumer capacity</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -655,10 +650,9 @@
           <t>What is the utility to mirror data between clusters?</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MirrorMaker (or Kafka MirrorMaker)</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -685,7 +679,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B) Log directory usage per broker</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -705,10 +699,9 @@
           <t>What is the preferred backup strategy for Kafka?</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Replication and mirroring, not traditional backups</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -728,10 +721,9 @@
           <t>A disk is filling up quickly. What two operational changes can you make without downtime?</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1) Reduce retention time 2) Add more brokers and reassign partitions</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -758,7 +750,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B) kafka-reassign-partitions</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -778,10 +770,9 @@
           <t>What command is used to delete a consumer group?</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>kafka-consumer-groups --delete</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -808,7 +799,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B) Rolling upgrade</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -828,10 +819,9 @@
           <t>A broker fails and cannot be recovered. How do you ensure the replicas on other brokers become leaders?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The controller will automatically elect new leaders from ISR</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -851,10 +841,9 @@
           <t>What metric indicates disk read operations per second?</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>kafka.log:type=LogFlushStats (or disk I/O metrics)</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -881,7 +870,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A) Stop brokers, then Zookeeper</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -901,10 +890,9 @@
           <t>What operational concept describes adding new brokers to increase capacity?</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Scaling out</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -924,10 +912,9 @@
           <t>You need to monitor if any brokers are under-replicated. What command gives you this information?</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>kafka-topics --describe --under-replicated-partitions</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
